--- a/backend/resumes.xlsx
+++ b/backend/resumes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1"/>
+  <dimension ref="A1:AP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,114 @@
       <c r="AP1" t="inlineStr">
         <is>
           <t>uploaded_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF MINNESOTA College of Design</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Bachelor of Science in Graphic Design</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Cumulative GPA 3.93, Dean's List, Twin cities Iron Range Scholarship</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>[{"employer": "AMERICAN EAGLE", "position": "Sales Associate", "duties": "Collaborated with the store merchandiser creating displays to attract clientele; Used trend awareness to assist customers; Inventory control; Processed shipment to increase product knowledge", "start_salary": null, "end_salary": null, "start_date": "07/2009", "end_date": null, "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}, {"employer": "PLANET BEACH", "position": "Spa Consultant", "duties": "Sell retail and memberships; Run all operating procedures; Communicate with clients; Attend promotional events; Handle cash and deposits; Received employee of the month award twice", "start_salary": null, "end_salary": null, "start_date": "08/2008", "end_date": null, "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}, {"employer": "HEARTBREAKER", "position": "Sales Associate", "duties": "Stocked sales floor with fast fashion inventory; Marked down items; Offered advice and assistance to guests", "start_salary": null, "end_salary": null, "start_date": "05/2008", "end_date": "08/2008", "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}, {"employer": "VICTORIA'S SECRET", "position": "Fashion Representative", "duties": "Assisted in training coworkers; Set up mannequins and displays; Provided customer service; Took seasonal inventory", "start_salary": null, "end_salary": null, "start_date": "01/2006", "end_date": "02/2009", "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}, {"employer": "TARGET CORPORATION", "position": "Brand Ambassador", "duties": "Represented Periscope Marketing and Target Inc. at a college event; Engaged University of Minnesota freshman in the Target brand experience", "start_salary": null, "end_salary": null, "start_date": "08/2009", "end_date": "08/2009", "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}]</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Resume_logo.jpeg</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>05/19/2026 05:22:43 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>(555) 555-5555</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>yourname@student.vhs.org</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Virginia Valley High School</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Winner of the State Math Competition (2024); Received municipal scholarship for academic excellence (2023); Completed a science and technology program for high school students (2022)</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>[{"employer": "Hardware Supply", "position": "Office Assistant", "duties": null, "start_salary": null, "end_salary": null, "start_date": null, "end_date": null, "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}, {"employer": null, "position": "Teaching Assistant", "duties": null, "start_salary": null, "end_salary": null, "start_date": null, "end_date": null, "supervisor": null, "contact_person": null, "reason_for_leaving": null, "street_number": null, "street_name": null, "suite": null, "city": null, "state": null, "zip": null, "phone": null, "email": null}]</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>resume_format_blog_asset-2.jpg</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>05/19/2026 05:25:01 PM</t>
         </is>
       </c>
     </row>
